--- a/LTMindtree M&A Analysis.xlsx
+++ b/LTMindtree M&A Analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avira\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED33CC64-88AB-495F-A034-7501B99CE634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CADBC9D-7EB7-4158-96B8-0ACB38B61F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Executive Dashboard" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="216">
   <si>
     <t>DEAL OVERVIEW</t>
   </si>
@@ -765,6 +765,9 @@
   </si>
   <si>
     <t>Strategic &amp; Financial Analysis | Synergy &amp; Post-Acquisition Value Creation Analysis</t>
+  </si>
+  <si>
+    <t>Risk</t>
   </si>
 </sst>
 </file>
@@ -1340,7 +1343,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="162">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1391,62 +1394,125 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="6" fillId="8" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="8" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="6" fillId="8" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="15" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="8" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="15" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="15" fillId="8" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1454,323 +1520,244 @@
     <xf numFmtId="10" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="15" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="8" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="10" fontId="8" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="15" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="6" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="6" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="15" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="6" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="6" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="6" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="15" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="15" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="15" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="15" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="6" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="15" fontId="15" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="6" fillId="8" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="8" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="15" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="6" fillId="8" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="15" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="15" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="10" fontId="6" fillId="8" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="15" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="15" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="15" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="15" fillId="8" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="15" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="15" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2086,474 +2073,474 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
     </row>
     <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
     </row>
     <row r="3" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
     </row>
     <row r="4" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
+      <c r="B5" s="84"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="84"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="52" t="s">
+      <c r="B6" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="48"/>
-      <c r="D6" s="49"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="60"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="33" t="s">
+      <c r="F6" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="25"/>
-      <c r="H6" s="33" t="s">
+      <c r="G6" s="57"/>
+      <c r="H6" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="I6" s="25"/>
+      <c r="I6" s="57"/>
     </row>
     <row r="7" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="30"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="71"/>
       <c r="E7" s="1"/>
-      <c r="F7" s="24" t="s">
+      <c r="F7" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="25"/>
-      <c r="H7" s="24" t="s">
+      <c r="G7" s="57"/>
+      <c r="H7" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="I7" s="25"/>
+      <c r="I7" s="57"/>
     </row>
     <row r="8" spans="1:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="86">
         <v>43542</v>
       </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="36"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="88"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="33" t="s">
+      <c r="F8" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="G8" s="25"/>
-      <c r="H8" s="33" t="s">
+      <c r="G8" s="57"/>
+      <c r="H8" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="I8" s="25"/>
+      <c r="I8" s="57"/>
     </row>
     <row r="9" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="47">
+      <c r="B9" s="72">
         <v>43648</v>
       </c>
-      <c r="C9" s="48"/>
-      <c r="D9" s="49"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="60"/>
       <c r="E9" s="1"/>
-      <c r="F9" s="24" t="s">
+      <c r="F9" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="25"/>
-      <c r="H9" s="24" t="s">
+      <c r="G9" s="57"/>
+      <c r="H9" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="I9" s="25"/>
+      <c r="I9" s="57"/>
     </row>
     <row r="10" spans="1:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="30"/>
+      <c r="C10" s="70"/>
+      <c r="D10" s="71"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="33" t="s">
+      <c r="F10" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="25"/>
-      <c r="H10" s="33" t="s">
+      <c r="G10" s="57"/>
+      <c r="H10" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="25"/>
+      <c r="I10" s="57"/>
     </row>
     <row r="11" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="30"/>
+      <c r="C11" s="70"/>
+      <c r="D11" s="71"/>
       <c r="E11" s="11"/>
-      <c r="F11" s="24" t="s">
+      <c r="F11" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="G11" s="25"/>
-      <c r="H11" s="24" t="s">
+      <c r="G11" s="57"/>
+      <c r="H11" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="I11" s="25"/>
+      <c r="I11" s="57"/>
     </row>
     <row r="12" spans="1:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="52" t="s">
+      <c r="B12" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="48"/>
-      <c r="D12" s="49"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="60"/>
       <c r="E12" s="1"/>
-      <c r="F12" s="38" t="s">
+      <c r="F12" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="39"/>
-      <c r="H12" s="33" t="s">
+      <c r="G12" s="78"/>
+      <c r="H12" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="I12" s="25"/>
+      <c r="I12" s="57"/>
     </row>
     <row r="13" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="46">
+      <c r="B13" s="69">
         <v>0.60060000000000002</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="30"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="71"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="40">
+      <c r="F13" s="79">
         <v>0.15859999999999999</v>
       </c>
-      <c r="G13" s="25"/>
-      <c r="H13" s="41">
+      <c r="G13" s="57"/>
+      <c r="H13" s="80">
         <v>0.60060000000000002</v>
       </c>
-      <c r="I13" s="42"/>
+      <c r="I13" s="81"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A16" s="32" t="s">
+      <c r="A16" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="23"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
+      <c r="B16" s="62"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="62"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="62"/>
+      <c r="G16" s="62"/>
+      <c r="H16" s="62"/>
+      <c r="I16" s="62"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A17" s="37" t="s">
+      <c r="A17" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="23"/>
-      <c r="I17" s="23"/>
+      <c r="B17" s="62"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="62"/>
+      <c r="G17" s="62"/>
+      <c r="H17" s="62"/>
+      <c r="I17" s="62"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A18" s="50" t="s">
+      <c r="A18" s="74" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="23"/>
+      <c r="B18" s="62"/>
+      <c r="C18" s="62"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="62"/>
+      <c r="F18" s="62"/>
+      <c r="G18" s="62"/>
+      <c r="H18" s="62"/>
+      <c r="I18" s="62"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A19" s="37" t="s">
+      <c r="A19" s="73" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
-      <c r="I19" s="23"/>
+      <c r="B19" s="62"/>
+      <c r="C19" s="62"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="62"/>
+      <c r="G19" s="62"/>
+      <c r="H19" s="62"/>
+      <c r="I19" s="62"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A20" s="50" t="s">
+      <c r="A20" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="23"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="23"/>
-      <c r="I20" s="23"/>
+      <c r="B20" s="62"/>
+      <c r="C20" s="62"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="62"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A21" s="37" t="s">
+      <c r="A21" s="73" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
+      <c r="B21" s="62"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="62"/>
+      <c r="H21" s="62"/>
+      <c r="I21" s="62"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A22" s="50" t="s">
+      <c r="A22" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="62"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A23" s="37" t="s">
+      <c r="A23" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="23"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
+      <c r="B23" s="62"/>
+      <c r="C23" s="62"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="62"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="62"/>
+      <c r="H23" s="62"/>
+      <c r="I23" s="62"/>
     </row>
     <row r="25" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="32" t="s">
+      <c r="A25" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
+      <c r="B25" s="62"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="62"/>
+      <c r="F25" s="62"/>
+      <c r="G25" s="62"/>
+      <c r="H25" s="62"/>
+      <c r="I25" s="62"/>
     </row>
     <row r="26" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="53" t="s">
+      <c r="B26" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="23"/>
+      <c r="C26" s="62"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="62"/>
+      <c r="F26" s="62"/>
+      <c r="G26" s="62"/>
+      <c r="H26" s="62"/>
+      <c r="I26" s="62"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27" s="13">
         <v>43542</v>
       </c>
-      <c r="B27" s="22" t="s">
+      <c r="B27" s="75" t="s">
         <v>43</v>
       </c>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="23"/>
+      <c r="C27" s="62"/>
+      <c r="D27" s="62"/>
+      <c r="E27" s="62"/>
+      <c r="F27" s="62"/>
+      <c r="G27" s="62"/>
+      <c r="H27" s="62"/>
+      <c r="I27" s="62"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28" s="13">
         <v>43559</v>
       </c>
-      <c r="B28" s="22" t="s">
+      <c r="B28" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
+      <c r="C28" s="62"/>
+      <c r="D28" s="62"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="62"/>
+      <c r="H28" s="62"/>
+      <c r="I28" s="62"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29" s="13">
         <v>43633</v>
       </c>
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="23"/>
+      <c r="C29" s="62"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="62"/>
+      <c r="F29" s="62"/>
+      <c r="G29" s="62"/>
+      <c r="H29" s="62"/>
+      <c r="I29" s="62"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30" s="13">
         <v>43642</v>
       </c>
-      <c r="B30" s="22" t="s">
+      <c r="B30" s="75" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="23"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="23"/>
-      <c r="H30" s="23"/>
-      <c r="I30" s="23"/>
+      <c r="C30" s="62"/>
+      <c r="D30" s="62"/>
+      <c r="E30" s="62"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="62"/>
+      <c r="H30" s="62"/>
+      <c r="I30" s="62"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A31" s="13">
         <v>43648</v>
       </c>
-      <c r="B31" s="22" t="s">
+      <c r="B31" s="75" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="23"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
-      <c r="I31" s="23"/>
+      <c r="C31" s="62"/>
+      <c r="D31" s="62"/>
+      <c r="E31" s="62"/>
+      <c r="F31" s="62"/>
+      <c r="G31" s="62"/>
+      <c r="H31" s="62"/>
+      <c r="I31" s="62"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32" s="18"/>
       <c r="B32" s="18"/>
     </row>
     <row r="34" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="32" t="s">
+      <c r="A34" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="B34" s="23"/>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="23"/>
-      <c r="H34" s="23"/>
-      <c r="I34" s="23"/>
+      <c r="B34" s="62"/>
+      <c r="C34" s="62"/>
+      <c r="D34" s="62"/>
+      <c r="E34" s="62"/>
+      <c r="F34" s="62"/>
+      <c r="G34" s="62"/>
+      <c r="H34" s="62"/>
+      <c r="I34" s="62"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A35" s="43" t="s">
+      <c r="A35" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="44"/>
-      <c r="C35" s="44"/>
-      <c r="D35" s="44"/>
-      <c r="E35" s="44"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="44"/>
-      <c r="H35" s="44"/>
-      <c r="I35" s="45"/>
+      <c r="B35" s="67"/>
+      <c r="C35" s="67"/>
+      <c r="D35" s="67"/>
+      <c r="E35" s="67"/>
+      <c r="F35" s="67"/>
+      <c r="G35" s="67"/>
+      <c r="H35" s="67"/>
+      <c r="I35" s="68"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A36" s="43" t="s">
+      <c r="A36" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="B36" s="44"/>
-      <c r="C36" s="44"/>
-      <c r="D36" s="44"/>
-      <c r="E36" s="44"/>
-      <c r="F36" s="44"/>
-      <c r="G36" s="44"/>
-      <c r="H36" s="44"/>
-      <c r="I36" s="45"/>
+      <c r="B36" s="67"/>
+      <c r="C36" s="67"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="67"/>
+      <c r="F36" s="67"/>
+      <c r="G36" s="67"/>
+      <c r="H36" s="67"/>
+      <c r="I36" s="68"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A37" s="43" t="s">
+      <c r="A37" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="B37" s="44"/>
-      <c r="C37" s="44"/>
-      <c r="D37" s="44"/>
-      <c r="E37" s="44"/>
-      <c r="F37" s="44"/>
-      <c r="G37" s="44"/>
-      <c r="H37" s="44"/>
-      <c r="I37" s="45"/>
+      <c r="B37" s="67"/>
+      <c r="C37" s="67"/>
+      <c r="D37" s="67"/>
+      <c r="E37" s="67"/>
+      <c r="F37" s="67"/>
+      <c r="G37" s="67"/>
+      <c r="H37" s="67"/>
+      <c r="I37" s="68"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A38" s="17" t="s">
@@ -2569,30 +2556,30 @@
       <c r="I38" s="16"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A39" s="43" t="s">
+      <c r="A39" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="B39" s="44"/>
-      <c r="C39" s="44"/>
-      <c r="D39" s="44"/>
-      <c r="E39" s="44"/>
-      <c r="F39" s="44"/>
-      <c r="G39" s="44"/>
-      <c r="H39" s="44"/>
-      <c r="I39" s="45"/>
+      <c r="B39" s="67"/>
+      <c r="C39" s="67"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="67"/>
+      <c r="F39" s="67"/>
+      <c r="G39" s="67"/>
+      <c r="H39" s="67"/>
+      <c r="I39" s="68"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A40" s="43" t="s">
+      <c r="A40" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="B40" s="44"/>
-      <c r="C40" s="44"/>
-      <c r="D40" s="44"/>
-      <c r="E40" s="44"/>
-      <c r="F40" s="44"/>
-      <c r="G40" s="44"/>
-      <c r="H40" s="44"/>
-      <c r="I40" s="45"/>
+      <c r="B40" s="67"/>
+      <c r="C40" s="67"/>
+      <c r="D40" s="67"/>
+      <c r="E40" s="67"/>
+      <c r="F40" s="67"/>
+      <c r="G40" s="67"/>
+      <c r="H40" s="67"/>
+      <c r="I40" s="68"/>
     </row>
     <row r="41" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="4"/>
@@ -2609,18 +2596,24 @@
     <row r="53" ht="38" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A16:I16"/>
-    <mergeCell ref="B26:I26"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B29:I29"/>
+    <mergeCell ref="B27:I27"/>
+    <mergeCell ref="B28:I28"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="B31:I31"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="B8:D8"/>
     <mergeCell ref="A37:I37"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="A40:I40"/>
@@ -2637,28 +2630,22 @@
     <mergeCell ref="A34:I34"/>
     <mergeCell ref="B30:I30"/>
     <mergeCell ref="H9:I9"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="B26:I26"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F6:G6"/>
     <mergeCell ref="A21:I21"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="F12:G12"/>
-    <mergeCell ref="B28:I28"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="B31:I31"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="B8:D8"/>
     <mergeCell ref="A19:I19"/>
-    <mergeCell ref="B29:I29"/>
-    <mergeCell ref="B27:I27"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="portrait"/>
@@ -2675,84 +2662,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
     </row>
     <row r="2" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
     </row>
     <row r="3" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A4" s="55" t="s">
+      <c r="A4" s="95" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="95"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="95"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A5" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="70" t="s">
+      <c r="B5" s="89" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="64"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="70" t="s">
+      <c r="C5" s="90"/>
+      <c r="D5" s="91"/>
+      <c r="E5" s="89" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="64"/>
-      <c r="G5" s="65"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="91"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A6" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="66">
+      <c r="B6" s="92">
         <v>1938</v>
       </c>
-      <c r="C6" s="67"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="66">
+      <c r="C6" s="93"/>
+      <c r="D6" s="94"/>
+      <c r="E6" s="92">
         <v>1999</v>
       </c>
-      <c r="F6" s="67"/>
-      <c r="G6" s="68"/>
+      <c r="F6" s="93"/>
+      <c r="G6" s="94"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="N6" s="3"/>
@@ -2761,16 +2748,16 @@
       <c r="A7" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="72" t="s">
+      <c r="B7" s="103" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="73"/>
-      <c r="D7" s="74"/>
-      <c r="E7" s="60" t="s">
+      <c r="C7" s="104"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="97" t="s">
         <v>59</v>
       </c>
-      <c r="F7" s="61"/>
-      <c r="G7" s="62"/>
+      <c r="F7" s="98"/>
+      <c r="G7" s="99"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="N7" s="3"/>
@@ -2779,16 +2766,16 @@
       <c r="A8" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="63" t="s">
+      <c r="B8" s="100" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="64"/>
-      <c r="D8" s="65"/>
-      <c r="E8" s="63" t="s">
+      <c r="C8" s="90"/>
+      <c r="D8" s="91"/>
+      <c r="E8" s="100" t="s">
         <v>62</v>
       </c>
-      <c r="F8" s="64"/>
-      <c r="G8" s="65"/>
+      <c r="F8" s="90"/>
+      <c r="G8" s="91"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="N8" s="3"/>
@@ -2797,16 +2784,16 @@
       <c r="A9" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B9" s="66" t="s">
+      <c r="B9" s="92" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="67"/>
-      <c r="D9" s="68"/>
-      <c r="E9" s="66" t="s">
+      <c r="C9" s="93"/>
+      <c r="D9" s="94"/>
+      <c r="E9" s="92" t="s">
         <v>65</v>
       </c>
-      <c r="F9" s="67"/>
-      <c r="G9" s="68"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="94"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="N9" s="3"/>
@@ -2815,16 +2802,16 @@
       <c r="A10" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B10" s="69" t="s">
+      <c r="B10" s="101" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="67"/>
-      <c r="D10" s="68"/>
-      <c r="E10" s="69" t="s">
+      <c r="C10" s="93"/>
+      <c r="D10" s="94"/>
+      <c r="E10" s="101" t="s">
         <v>68</v>
       </c>
-      <c r="F10" s="67"/>
-      <c r="G10" s="68"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="94"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="N10" s="3"/>
@@ -2833,16 +2820,16 @@
       <c r="A11" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="B11" s="70" t="s">
+      <c r="B11" s="89" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="64"/>
-      <c r="D11" s="65"/>
-      <c r="E11" s="70" t="s">
+      <c r="C11" s="90"/>
+      <c r="D11" s="91"/>
+      <c r="E11" s="89" t="s">
         <v>71</v>
       </c>
-      <c r="F11" s="64"/>
-      <c r="G11" s="65"/>
+      <c r="F11" s="90"/>
+      <c r="G11" s="91"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="N11" s="3"/>
@@ -2851,224 +2838,233 @@
       <c r="A12" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="B12" s="71" t="s">
+      <c r="B12" s="102" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="67"/>
-      <c r="D12" s="68"/>
-      <c r="E12" s="71" t="s">
+      <c r="C12" s="93"/>
+      <c r="D12" s="94"/>
+      <c r="E12" s="102" t="s">
         <v>74</v>
       </c>
-      <c r="F12" s="67"/>
-      <c r="G12" s="68"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="94"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="N12" s="3"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A15" s="55" t="s">
+      <c r="A15" s="95" t="s">
         <v>100</v>
       </c>
-      <c r="B15" s="55"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="55"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="95"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A16" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B16" s="57" t="s">
+      <c r="B16" s="108" t="s">
         <v>81</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="57" t="s">
+      <c r="C16" s="108"/>
+      <c r="D16" s="108"/>
+      <c r="E16" s="108" t="s">
         <v>82</v>
       </c>
-      <c r="F16" s="57"/>
-      <c r="G16" s="57"/>
+      <c r="F16" s="108"/>
+      <c r="G16" s="108"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="B17" s="56" t="s">
+      <c r="B17" s="107" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="56"/>
-      <c r="D17" s="56"/>
-      <c r="E17" s="56" t="s">
+      <c r="C17" s="107"/>
+      <c r="D17" s="107"/>
+      <c r="E17" s="107" t="s">
         <v>85</v>
       </c>
-      <c r="F17" s="56"/>
-      <c r="G17" s="56"/>
+      <c r="F17" s="107"/>
+      <c r="G17" s="107"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="B18" s="56" t="s">
+      <c r="B18" s="107" t="s">
         <v>87</v>
       </c>
-      <c r="C18" s="56"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="56" t="s">
+      <c r="C18" s="107"/>
+      <c r="D18" s="107"/>
+      <c r="E18" s="107" t="s">
         <v>88</v>
       </c>
-      <c r="F18" s="56"/>
-      <c r="G18" s="56"/>
+      <c r="F18" s="107"/>
+      <c r="G18" s="107"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B19" s="56" t="s">
+      <c r="B19" s="107" t="s">
         <v>90</v>
       </c>
-      <c r="C19" s="56"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="56" t="s">
+      <c r="C19" s="107"/>
+      <c r="D19" s="107"/>
+      <c r="E19" s="107" t="s">
         <v>91</v>
       </c>
-      <c r="F19" s="56"/>
-      <c r="G19" s="56"/>
+      <c r="F19" s="107"/>
+      <c r="G19" s="107"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="B20" s="56" t="s">
+      <c r="B20" s="107" t="s">
         <v>93</v>
       </c>
-      <c r="C20" s="56"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="56" t="s">
+      <c r="C20" s="107"/>
+      <c r="D20" s="107"/>
+      <c r="E20" s="107" t="s">
         <v>93</v>
       </c>
-      <c r="F20" s="56"/>
-      <c r="G20" s="56"/>
+      <c r="F20" s="107"/>
+      <c r="G20" s="107"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="B21" s="56" t="s">
+      <c r="B21" s="107" t="s">
         <v>95</v>
       </c>
-      <c r="C21" s="56"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="56" t="s">
+      <c r="C21" s="107"/>
+      <c r="D21" s="107"/>
+      <c r="E21" s="107" t="s">
         <v>96</v>
       </c>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
+      <c r="F21" s="107"/>
+      <c r="G21" s="107"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="B22" s="56" t="s">
+      <c r="B22" s="107" t="s">
         <v>98</v>
       </c>
-      <c r="C22" s="56"/>
-      <c r="D22" s="56"/>
-      <c r="E22" s="56" t="s">
+      <c r="C22" s="107"/>
+      <c r="D22" s="107"/>
+      <c r="E22" s="107" t="s">
         <v>99</v>
       </c>
-      <c r="F22" s="56"/>
-      <c r="G22" s="56"/>
+      <c r="F22" s="107"/>
+      <c r="G22" s="107"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A25" s="32" t="s">
+      <c r="A25" s="61" t="s">
         <v>101</v>
       </c>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
+      <c r="B25" s="62"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="62"/>
+      <c r="F25" s="62"/>
+      <c r="G25" s="62"/>
+      <c r="H25" s="62"/>
+      <c r="I25" s="62"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A26" s="58" t="s">
+      <c r="A26" s="96" t="s">
         <v>75</v>
       </c>
-      <c r="B26" s="58"/>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="58"/>
+      <c r="B26" s="96"/>
+      <c r="C26" s="96"/>
+      <c r="D26" s="96"/>
+      <c r="E26" s="96"/>
+      <c r="F26" s="96"/>
+      <c r="G26" s="96"/>
+      <c r="H26" s="96"/>
+      <c r="I26" s="96"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A27" s="59" t="s">
+      <c r="A27" s="106" t="s">
         <v>76</v>
       </c>
-      <c r="B27" s="59"/>
-      <c r="C27" s="59"/>
-      <c r="D27" s="59"/>
-      <c r="E27" s="59"/>
-      <c r="F27" s="59"/>
-      <c r="G27" s="59"/>
-      <c r="H27" s="59"/>
-      <c r="I27" s="59"/>
+      <c r="B27" s="106"/>
+      <c r="C27" s="106"/>
+      <c r="D27" s="106"/>
+      <c r="E27" s="106"/>
+      <c r="F27" s="106"/>
+      <c r="G27" s="106"/>
+      <c r="H27" s="106"/>
+      <c r="I27" s="106"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A28" s="58" t="s">
+      <c r="A28" s="96" t="s">
         <v>77</v>
       </c>
-      <c r="B28" s="58"/>
-      <c r="C28" s="58"/>
-      <c r="D28" s="58"/>
-      <c r="E28" s="58"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="58"/>
-      <c r="I28" s="58"/>
+      <c r="B28" s="96"/>
+      <c r="C28" s="96"/>
+      <c r="D28" s="96"/>
+      <c r="E28" s="96"/>
+      <c r="F28" s="96"/>
+      <c r="G28" s="96"/>
+      <c r="H28" s="96"/>
+      <c r="I28" s="96"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A29" s="59" t="s">
+      <c r="A29" s="106" t="s">
         <v>78</v>
       </c>
-      <c r="B29" s="59"/>
-      <c r="C29" s="59"/>
-      <c r="D29" s="59"/>
-      <c r="E29" s="59"/>
-      <c r="F29" s="59"/>
-      <c r="G29" s="59"/>
-      <c r="H29" s="59"/>
-      <c r="I29" s="59"/>
+      <c r="B29" s="106"/>
+      <c r="C29" s="106"/>
+      <c r="D29" s="106"/>
+      <c r="E29" s="106"/>
+      <c r="F29" s="106"/>
+      <c r="G29" s="106"/>
+      <c r="H29" s="106"/>
+      <c r="I29" s="106"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A30" s="58" t="s">
+      <c r="A30" s="96" t="s">
         <v>79</v>
       </c>
-      <c r="B30" s="58"/>
-      <c r="C30" s="58"/>
-      <c r="D30" s="58"/>
-      <c r="E30" s="58"/>
-      <c r="F30" s="58"/>
-      <c r="G30" s="58"/>
-      <c r="H30" s="58"/>
-      <c r="I30" s="58"/>
+      <c r="B30" s="96"/>
+      <c r="C30" s="96"/>
+      <c r="D30" s="96"/>
+      <c r="E30" s="96"/>
+      <c r="F30" s="96"/>
+      <c r="G30" s="96"/>
+      <c r="H30" s="96"/>
+      <c r="I30" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E16:G16"/>
     <mergeCell ref="A30:I30"/>
     <mergeCell ref="E7:G7"/>
     <mergeCell ref="E8:G8"/>
@@ -3085,23 +3081,14 @@
     <mergeCell ref="A25:I25"/>
     <mergeCell ref="A26:I26"/>
     <mergeCell ref="A27:I27"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="A29:I29"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="A4:G4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3121,444 +3108,461 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="34.15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
     </row>
     <row r="2" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="65" t="s">
         <v>102</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
     </row>
     <row r="3" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="78"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="23"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A5" s="99" t="s">
+      <c r="A5" s="132" t="s">
         <v>123</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="F5" s="100" t="s">
+      <c r="B5" s="84"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="84"/>
+      <c r="F5" s="128" t="s">
         <v>124</v>
       </c>
-      <c r="G5" s="93"/>
-      <c r="H5" s="93"/>
-      <c r="I5" s="93"/>
+      <c r="G5" s="129"/>
+      <c r="H5" s="129"/>
+      <c r="I5" s="129"/>
       <c r="N5" s="3"/>
-      <c r="O5" s="77"/>
+      <c r="O5" s="22"/>
     </row>
     <row r="6" spans="1:15" ht="25.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="90" t="s">
+      <c r="A6" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="B6" s="92" t="s">
+      <c r="B6" s="118" t="s">
         <v>103</v>
       </c>
-      <c r="C6" s="82"/>
-      <c r="D6" s="82"/>
-      <c r="F6" s="90" t="s">
+      <c r="C6" s="119"/>
+      <c r="D6" s="119"/>
+      <c r="F6" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="G6" s="92" t="s">
+      <c r="G6" s="118" t="s">
         <v>103</v>
       </c>
-      <c r="H6" s="82"/>
-      <c r="I6" s="82"/>
+      <c r="H6" s="119"/>
+      <c r="I6" s="119"/>
       <c r="N6" s="3"/>
-      <c r="O6" s="77"/>
+      <c r="O6" s="22"/>
     </row>
     <row r="7" spans="1:15" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A7" s="115" t="s">
+      <c r="A7" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="B7" s="83" t="s">
+      <c r="B7" s="113" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="88"/>
-      <c r="D7" s="88"/>
-      <c r="F7" s="119" t="s">
+      <c r="C7" s="110"/>
+      <c r="D7" s="110"/>
+      <c r="F7" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="G7" s="83" t="s">
+      <c r="G7" s="113" t="s">
         <v>71</v>
       </c>
-      <c r="H7" s="88"/>
-      <c r="I7" s="88"/>
+      <c r="H7" s="110"/>
+      <c r="I7" s="110"/>
       <c r="N7" s="3"/>
-      <c r="O7" s="77"/>
+      <c r="O7" s="22"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A8" s="116" t="s">
+      <c r="A8" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="85" t="s">
+      <c r="B8" s="131" t="s">
         <v>105</v>
       </c>
-      <c r="C8" s="88"/>
-      <c r="D8" s="88"/>
-      <c r="F8" s="119" t="s">
+      <c r="C8" s="110"/>
+      <c r="D8" s="110"/>
+      <c r="F8" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="G8" s="85" t="s">
+      <c r="G8" s="131" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="88"/>
-      <c r="I8" s="88"/>
-      <c r="M8" s="76"/>
+      <c r="H8" s="110"/>
+      <c r="I8" s="110"/>
+      <c r="M8" s="21"/>
       <c r="N8" s="3"/>
-      <c r="O8" s="77"/>
+      <c r="O8" s="22"/>
     </row>
     <row r="9" spans="1:15" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A9" s="116" t="s">
+      <c r="A9" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="B9" s="86">
+      <c r="B9" s="111">
         <v>0.20319999999999999</v>
       </c>
-      <c r="C9" s="88"/>
-      <c r="D9" s="88"/>
-      <c r="F9" s="119" t="s">
+      <c r="C9" s="110"/>
+      <c r="D9" s="110"/>
+      <c r="F9" s="38" t="s">
         <v>116</v>
       </c>
-      <c r="G9" s="86" t="s">
+      <c r="G9" s="111" t="s">
         <v>117</v>
       </c>
-      <c r="H9" s="88"/>
-      <c r="I9" s="88"/>
+      <c r="H9" s="110"/>
+      <c r="I9" s="110"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
-      <c r="O9" s="77"/>
+      <c r="O9" s="22"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A10" s="115" t="s">
+      <c r="A10" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="B10" s="83" t="s">
+      <c r="B10" s="113" t="s">
         <v>108</v>
       </c>
-      <c r="C10" s="88"/>
-      <c r="D10" s="88"/>
-      <c r="F10" s="119" t="s">
+      <c r="C10" s="110"/>
+      <c r="D10" s="110"/>
+      <c r="F10" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="83" t="s">
+      <c r="G10" s="113" t="s">
         <v>118</v>
       </c>
-      <c r="H10" s="88"/>
-      <c r="I10" s="88"/>
+      <c r="H10" s="110"/>
+      <c r="I10" s="110"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
-      <c r="O10" s="77"/>
+      <c r="O10" s="22"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A11" s="115" t="s">
+      <c r="A11" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="B11" s="86">
+      <c r="B11" s="111">
         <v>0.31</v>
       </c>
-      <c r="C11" s="91"/>
-      <c r="D11" s="91"/>
-      <c r="F11" s="119" t="s">
+      <c r="C11" s="130"/>
+      <c r="D11" s="130"/>
+      <c r="F11" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="G11" s="86" t="s">
+      <c r="G11" s="111" t="s">
         <v>120</v>
       </c>
-      <c r="H11" s="91"/>
-      <c r="I11" s="91"/>
+      <c r="H11" s="130"/>
+      <c r="I11" s="130"/>
       <c r="M11" s="3"/>
-      <c r="N11" s="79"/>
+      <c r="N11" s="24"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A12" s="115" t="s">
+      <c r="A12" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="B12" s="86">
+      <c r="B12" s="111">
         <v>0.60060000000000002</v>
       </c>
-      <c r="C12" s="91"/>
-      <c r="D12" s="91"/>
-      <c r="E12" s="80"/>
-      <c r="F12" s="119" t="s">
+      <c r="C12" s="130"/>
+      <c r="D12" s="130"/>
+      <c r="F12" s="38" t="s">
         <v>121</v>
       </c>
-      <c r="G12" s="86" t="s">
+      <c r="G12" s="111" t="s">
         <v>122</v>
       </c>
-      <c r="H12" s="91"/>
-      <c r="I12" s="91"/>
+      <c r="H12" s="130"/>
+      <c r="I12" s="130"/>
       <c r="M12" s="3"/>
-      <c r="N12" s="77"/>
+      <c r="N12" s="22"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A13" s="117" t="s">
+      <c r="A13" s="36" t="s">
         <v>111</v>
       </c>
-      <c r="B13" s="86" t="s">
+      <c r="B13" s="111" t="s">
         <v>112</v>
       </c>
-      <c r="C13" s="88"/>
-      <c r="D13" s="88"/>
-      <c r="E13" s="80"/>
-      <c r="F13" s="94"/>
-      <c r="G13" s="95"/>
-      <c r="H13" s="96"/>
-      <c r="I13" s="96"/>
+      <c r="C13" s="110"/>
+      <c r="D13" s="110"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="125"/>
+      <c r="H13" s="115"/>
+      <c r="I13" s="115"/>
       <c r="M13" s="3"/>
-      <c r="N13" s="79"/>
+      <c r="N13" s="24"/>
     </row>
     <row r="14" spans="1:15" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A14" s="118" t="s">
+      <c r="A14" s="37" t="s">
         <v>113</v>
       </c>
-      <c r="B14" s="89" t="s">
+      <c r="B14" s="126" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="89"/>
-      <c r="D14" s="89"/>
-      <c r="E14" s="80"/>
-      <c r="F14" s="97"/>
-      <c r="G14" s="98"/>
-      <c r="H14" s="98"/>
-      <c r="I14" s="98"/>
+      <c r="C14" s="126"/>
+      <c r="D14" s="126"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="127"/>
+      <c r="H14" s="127"/>
+      <c r="I14" s="127"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="79"/>
+      <c r="N14" s="24"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="D15" s="80"/>
-      <c r="F15" s="80"/>
-      <c r="G15" s="80"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="77"/>
+      <c r="N15" s="22"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="C16" s="80"/>
-      <c r="D16" s="80"/>
-      <c r="E16" s="80"/>
-      <c r="F16" s="80"/>
-      <c r="G16" s="80"/>
-      <c r="H16" s="80"/>
-      <c r="I16" s="80"/>
-      <c r="J16" s="80"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="77"/>
+      <c r="N16" s="22"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A17" s="100" t="s">
+      <c r="A17" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="B17" s="93"/>
-      <c r="C17" s="93"/>
-      <c r="D17" s="93"/>
-      <c r="F17" s="100" t="s">
+      <c r="B17" s="129"/>
+      <c r="C17" s="129"/>
+      <c r="D17" s="129"/>
+      <c r="F17" s="128" t="s">
         <v>126</v>
       </c>
-      <c r="G17" s="93"/>
-      <c r="H17" s="93"/>
-      <c r="I17" s="93"/>
-      <c r="N17" s="76"/>
-      <c r="O17" s="76"/>
-      <c r="P17" s="78"/>
+      <c r="G17" s="129"/>
+      <c r="H17" s="129"/>
+      <c r="I17" s="129"/>
+      <c r="N17" s="21"/>
+      <c r="O17" s="21"/>
+      <c r="P17" s="23"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A18" s="90" t="s">
+      <c r="A18" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="92" t="s">
+      <c r="B18" s="118" t="s">
         <v>103</v>
       </c>
-      <c r="C18" s="82"/>
-      <c r="D18" s="82"/>
-      <c r="F18" s="111" t="s">
+      <c r="C18" s="119"/>
+      <c r="D18" s="119"/>
+      <c r="F18" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="G18" s="92" t="s">
+      <c r="G18" s="118" t="s">
         <v>103</v>
       </c>
-      <c r="H18" s="82"/>
-      <c r="I18" s="82"/>
+      <c r="H18" s="119"/>
+      <c r="I18" s="119"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
-      <c r="P18" s="101"/>
+      <c r="P18" s="32"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A19" s="119" t="s">
+      <c r="A19" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="B19" s="107">
+      <c r="B19" s="120">
         <v>846</v>
       </c>
-      <c r="C19" s="104"/>
-      <c r="D19" s="105"/>
-      <c r="F19" s="119" t="s">
+      <c r="C19" s="121"/>
+      <c r="D19" s="122"/>
+      <c r="F19" s="38" t="s">
         <v>132</v>
       </c>
-      <c r="G19" s="106" t="s">
+      <c r="G19" s="112" t="s">
         <v>32</v>
       </c>
-      <c r="H19" s="88"/>
-      <c r="I19" s="88"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="110"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-      <c r="P19" s="101"/>
+      <c r="P19" s="32"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A20" s="119" t="s">
+      <c r="A20" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="B20" s="108">
+      <c r="B20" s="123">
         <v>980</v>
       </c>
-      <c r="C20" s="88"/>
-      <c r="D20" s="88"/>
-      <c r="F20" s="119" t="s">
+      <c r="C20" s="110"/>
+      <c r="D20" s="110"/>
+      <c r="F20" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="G20" s="112" t="s">
+      <c r="G20" s="124" t="s">
         <v>33</v>
       </c>
-      <c r="H20" s="88"/>
-      <c r="I20" s="88"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="110"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
-      <c r="P20" s="102"/>
+      <c r="P20" s="33"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A21" s="119" t="s">
+      <c r="A21" s="38" t="s">
         <v>128</v>
       </c>
-      <c r="B21" s="86">
+      <c r="B21" s="111">
         <v>0.15840000000000001</v>
       </c>
-      <c r="C21" s="88"/>
-      <c r="D21" s="88"/>
-      <c r="F21" s="119" t="s">
+      <c r="C21" s="110"/>
+      <c r="D21" s="110"/>
+      <c r="F21" s="38" t="s">
         <v>133</v>
       </c>
-      <c r="G21" s="113" t="s">
+      <c r="G21" s="112" t="s">
         <v>134</v>
       </c>
-      <c r="H21" s="114"/>
-      <c r="I21" s="114"/>
+      <c r="H21" s="110"/>
+      <c r="I21" s="110"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
-      <c r="P21" s="77"/>
+      <c r="P21" s="22"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A22" s="119" t="s">
+      <c r="A22" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="B22" s="83" t="s">
+      <c r="B22" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="C22" s="88"/>
-      <c r="D22" s="88"/>
-      <c r="F22" s="109"/>
-      <c r="G22" s="110"/>
-      <c r="H22" s="96"/>
-      <c r="I22" s="96"/>
+      <c r="C22" s="110"/>
+      <c r="D22" s="110"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="114"/>
+      <c r="H22" s="115"/>
+      <c r="I22" s="115"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A25" s="120" t="s">
+      <c r="A25" s="116" t="s">
         <v>135</v>
       </c>
-      <c r="B25" s="84"/>
-      <c r="C25" s="84"/>
-      <c r="D25" s="84"/>
-      <c r="E25" s="84"/>
-      <c r="F25" s="84"/>
-      <c r="G25" s="84"/>
-      <c r="H25" s="84"/>
-      <c r="I25" s="84"/>
+      <c r="B25" s="117"/>
+      <c r="C25" s="117"/>
+      <c r="D25" s="117"/>
+      <c r="E25" s="117"/>
+      <c r="F25" s="117"/>
+      <c r="G25" s="117"/>
+      <c r="H25" s="117"/>
+      <c r="I25" s="117"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A26" s="121" t="s">
+      <c r="A26" s="110" t="s">
         <v>138</v>
       </c>
-      <c r="B26" s="121"/>
-      <c r="C26" s="121"/>
-      <c r="D26" s="121"/>
-      <c r="E26" s="121"/>
-      <c r="F26" s="121"/>
-      <c r="G26" s="121"/>
-      <c r="H26" s="121"/>
-      <c r="I26" s="121"/>
+      <c r="B26" s="110"/>
+      <c r="C26" s="110"/>
+      <c r="D26" s="110"/>
+      <c r="E26" s="110"/>
+      <c r="F26" s="110"/>
+      <c r="G26" s="110"/>
+      <c r="H26" s="110"/>
+      <c r="I26" s="110"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A27" s="122" t="s">
+      <c r="A27" s="109" t="s">
         <v>139</v>
       </c>
-      <c r="B27" s="122"/>
-      <c r="C27" s="122"/>
-      <c r="D27" s="122"/>
-      <c r="E27" s="122"/>
-      <c r="F27" s="122"/>
-      <c r="G27" s="122"/>
-      <c r="H27" s="122"/>
-      <c r="I27" s="122"/>
+      <c r="B27" s="109"/>
+      <c r="C27" s="109"/>
+      <c r="D27" s="109"/>
+      <c r="E27" s="109"/>
+      <c r="F27" s="109"/>
+      <c r="G27" s="109"/>
+      <c r="H27" s="109"/>
+      <c r="I27" s="109"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A28" s="121" t="s">
+      <c r="A28" s="110" t="s">
         <v>136</v>
       </c>
-      <c r="B28" s="121"/>
-      <c r="C28" s="121"/>
-      <c r="D28" s="121"/>
-      <c r="E28" s="121"/>
-      <c r="F28" s="121"/>
-      <c r="G28" s="121"/>
-      <c r="H28" s="121"/>
-      <c r="I28" s="121"/>
+      <c r="B28" s="110"/>
+      <c r="C28" s="110"/>
+      <c r="D28" s="110"/>
+      <c r="E28" s="110"/>
+      <c r="F28" s="110"/>
+      <c r="G28" s="110"/>
+      <c r="H28" s="110"/>
+      <c r="I28" s="110"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A29" s="122" t="s">
+      <c r="A29" s="109" t="s">
         <v>137</v>
       </c>
-      <c r="B29" s="122"/>
-      <c r="C29" s="122"/>
-      <c r="D29" s="122"/>
-      <c r="E29" s="122"/>
-      <c r="F29" s="122"/>
-      <c r="G29" s="122"/>
-      <c r="H29" s="122"/>
-      <c r="I29" s="122"/>
+      <c r="B29" s="109"/>
+      <c r="C29" s="109"/>
+      <c r="D29" s="109"/>
+      <c r="E29" s="109"/>
+      <c r="F29" s="109"/>
+      <c r="G29" s="109"/>
+      <c r="H29" s="109"/>
+      <c r="I29" s="109"/>
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="G20:I20"/>
     <mergeCell ref="A27:I27"/>
     <mergeCell ref="A28:I28"/>
     <mergeCell ref="A29:I29"/>
@@ -3568,37 +3572,6 @@
     <mergeCell ref="G22:I22"/>
     <mergeCell ref="A25:I25"/>
     <mergeCell ref="A26:I26"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="G6:I6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3621,421 +3594,400 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="34.15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
     </row>
     <row r="2" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="144" t="s">
+      <c r="A2" s="145" t="s">
         <v>214</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
     </row>
     <row r="3" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
     </row>
     <row r="4" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="78"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="23"/>
     </row>
     <row r="5" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="130" t="s">
+      <c r="A5" s="146" t="s">
         <v>162</v>
       </c>
-      <c r="B5" s="130"/>
-      <c r="C5" s="130"/>
-      <c r="D5" s="130"/>
-      <c r="F5" s="100" t="s">
+      <c r="B5" s="146"/>
+      <c r="C5" s="146"/>
+      <c r="D5" s="146"/>
+      <c r="F5" s="128" t="s">
         <v>161</v>
       </c>
-      <c r="G5" s="93"/>
-      <c r="H5" s="93"/>
-      <c r="I5" s="93"/>
+      <c r="G5" s="129"/>
+      <c r="H5" s="129"/>
+      <c r="I5" s="129"/>
       <c r="N5" s="3"/>
-      <c r="O5" s="77"/>
+      <c r="O5" s="22"/>
     </row>
     <row r="6" spans="1:16" ht="25.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="111" t="s">
+      <c r="A6" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="B6" s="92" t="s">
+      <c r="B6" s="118" t="s">
         <v>141</v>
       </c>
-      <c r="C6" s="92"/>
-      <c r="D6" s="124" t="s">
+      <c r="C6" s="118"/>
+      <c r="D6" s="39" t="s">
         <v>142</v>
       </c>
-      <c r="F6" s="111" t="s">
+      <c r="F6" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="G6" s="92" t="s">
+      <c r="G6" s="118" t="s">
         <v>155</v>
       </c>
-      <c r="H6" s="82"/>
-      <c r="I6" s="82"/>
-      <c r="O6" s="77"/>
+      <c r="H6" s="119"/>
+      <c r="I6" s="119"/>
+      <c r="O6" s="22"/>
     </row>
     <row r="7" spans="1:16" ht="57" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="131" t="s">
+      <c r="A7" s="42" t="s">
         <v>143</v>
       </c>
-      <c r="B7" s="132" t="s">
+      <c r="B7" s="133" t="s">
         <v>144</v>
       </c>
-      <c r="C7" s="132"/>
-      <c r="D7" s="123" t="s">
+      <c r="C7" s="133"/>
+      <c r="D7" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="E7" s="133"/>
-      <c r="F7" s="119" t="s">
+      <c r="F7" s="38" t="s">
         <v>156</v>
       </c>
-      <c r="G7" s="134" t="s">
+      <c r="G7" s="139" t="s">
         <v>163</v>
       </c>
-      <c r="H7" s="127"/>
-      <c r="I7" s="127"/>
+      <c r="H7" s="117"/>
+      <c r="I7" s="117"/>
     </row>
     <row r="8" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="135" t="s">
+      <c r="A8" s="43" t="s">
         <v>143</v>
       </c>
-      <c r="B8" s="132" t="s">
+      <c r="B8" s="133" t="s">
         <v>145</v>
       </c>
-      <c r="C8" s="132"/>
-      <c r="D8" s="123" t="s">
+      <c r="C8" s="133"/>
+      <c r="D8" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="E8" s="133"/>
-      <c r="F8" s="119" t="s">
+      <c r="F8" s="38" t="s">
         <v>157</v>
       </c>
-      <c r="G8" s="136" t="s">
+      <c r="G8" s="140" t="s">
         <v>164</v>
       </c>
-      <c r="H8" s="127"/>
-      <c r="I8" s="127"/>
+      <c r="H8" s="117"/>
+      <c r="I8" s="117"/>
     </row>
     <row r="9" spans="1:16" ht="45.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="135" t="s">
+      <c r="A9" s="43" t="s">
         <v>143</v>
       </c>
-      <c r="B9" s="132" t="s">
+      <c r="B9" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="C9" s="132"/>
-      <c r="D9" s="123" t="s">
+      <c r="C9" s="133"/>
+      <c r="D9" s="25" t="s">
         <v>147</v>
       </c>
-      <c r="E9" s="133"/>
-      <c r="F9" s="119" t="s">
+      <c r="F9" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="G9" s="137" t="s">
+      <c r="G9" s="141" t="s">
         <v>165</v>
       </c>
-      <c r="H9" s="127"/>
-      <c r="I9" s="127"/>
+      <c r="H9" s="117"/>
+      <c r="I9" s="117"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A10" s="131" t="s">
+      <c r="A10" s="42" t="s">
         <v>148</v>
       </c>
-      <c r="B10" s="132" t="s">
+      <c r="B10" s="133" t="s">
         <v>149</v>
       </c>
-      <c r="C10" s="132"/>
-      <c r="D10" s="123" t="s">
+      <c r="C10" s="133"/>
+      <c r="D10" s="25" t="s">
         <v>147</v>
       </c>
-      <c r="E10" s="133"/>
-      <c r="F10" s="119" t="s">
+      <c r="F10" s="38" t="s">
         <v>159</v>
       </c>
-      <c r="G10" s="134" t="s">
+      <c r="G10" s="139" t="s">
         <v>166</v>
       </c>
-      <c r="H10" s="127"/>
-      <c r="I10" s="127"/>
+      <c r="H10" s="117"/>
+      <c r="I10" s="117"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A11" s="131" t="s">
+      <c r="A11" s="42" t="s">
         <v>148</v>
       </c>
-      <c r="B11" s="132" t="s">
+      <c r="B11" s="133" t="s">
         <v>150</v>
       </c>
-      <c r="C11" s="132"/>
-      <c r="D11" s="123" t="s">
+      <c r="C11" s="133"/>
+      <c r="D11" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="E11" s="133"/>
-      <c r="F11" s="119" t="s">
+      <c r="F11" s="38" t="s">
         <v>160</v>
       </c>
-      <c r="G11" s="137" t="s">
+      <c r="G11" s="141" t="s">
         <v>167</v>
       </c>
-      <c r="H11" s="138"/>
-      <c r="I11" s="138"/>
+      <c r="H11" s="142"/>
+      <c r="I11" s="142"/>
     </row>
     <row r="12" spans="1:16" ht="24.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="131" t="s">
+      <c r="A12" s="42" t="s">
         <v>151</v>
       </c>
-      <c r="B12" s="132" t="s">
+      <c r="B12" s="133" t="s">
         <v>152</v>
       </c>
-      <c r="C12" s="132"/>
-      <c r="D12" s="123" t="s">
+      <c r="C12" s="133"/>
+      <c r="D12" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="E12" s="133"/>
-      <c r="F12" s="139"/>
-      <c r="G12" s="140"/>
-      <c r="H12" s="141"/>
-      <c r="I12" s="141"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="143"/>
+      <c r="H12" s="144"/>
+      <c r="I12" s="144"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A13" s="142" t="s">
+      <c r="A13" s="46" t="s">
         <v>151</v>
       </c>
-      <c r="B13" s="132" t="s">
+      <c r="B13" s="133" t="s">
         <v>153</v>
       </c>
-      <c r="C13" s="132"/>
-      <c r="D13" s="123" t="s">
+      <c r="C13" s="133"/>
+      <c r="D13" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="E13" s="139"/>
-      <c r="F13" s="139"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="B14" s="128"/>
-      <c r="C14" s="128"/>
-      <c r="D14" s="126"/>
-      <c r="E14" s="126"/>
-      <c r="F14" s="97"/>
+      <c r="B14" s="134"/>
+      <c r="C14" s="134"/>
+      <c r="D14" s="135"/>
+      <c r="E14" s="135"/>
+      <c r="F14" s="31"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="D15" s="80"/>
-      <c r="F15" s="80"/>
-      <c r="G15" s="80"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="77"/>
+      <c r="N15" s="22"/>
     </row>
     <row r="16" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="148" t="s">
+      <c r="A16" s="137" t="s">
         <v>168</v>
       </c>
-      <c r="B16" s="129"/>
-      <c r="C16" s="129"/>
-      <c r="D16" s="129"/>
-      <c r="N16" s="76"/>
-      <c r="O16" s="76"/>
-      <c r="P16" s="78"/>
+      <c r="B16" s="138"/>
+      <c r="C16" s="138"/>
+      <c r="D16" s="138"/>
+      <c r="N16" s="21"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="23"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A17" s="111" t="s">
+      <c r="A17" s="29" t="s">
         <v>169</v>
       </c>
-      <c r="B17" s="124" t="s">
+      <c r="B17" s="39" t="s">
         <v>181</v>
       </c>
-      <c r="C17" s="124" t="s">
+      <c r="C17" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="D17" s="124" t="s">
+      <c r="D17" s="39" t="s">
         <v>176</v>
       </c>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
-      <c r="P17" s="101"/>
+      <c r="P17" s="32"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A18" s="119" t="s">
+      <c r="A18" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="B18" s="149">
+      <c r="B18" s="48">
         <v>7022</v>
       </c>
-      <c r="C18" s="150">
+      <c r="C18" s="49">
         <v>10900</v>
       </c>
-      <c r="D18" s="81" t="s">
+      <c r="D18" s="25" t="s">
         <v>182</v>
       </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
-      <c r="P18" s="101"/>
+      <c r="P18" s="32"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A19" s="119" t="s">
+      <c r="A19" s="38" t="s">
         <v>170</v>
       </c>
-      <c r="B19" s="147">
+      <c r="B19" s="44">
         <v>0.152</v>
       </c>
-      <c r="C19" s="151">
+      <c r="C19" s="50">
         <v>0.21</v>
       </c>
-      <c r="D19" s="81" t="s">
+      <c r="D19" s="25" t="s">
         <v>182</v>
       </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-      <c r="P19" s="102"/>
+      <c r="P19" s="33"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A20" s="119" t="s">
+      <c r="A20" s="38" t="s">
         <v>178</v>
       </c>
-      <c r="B20" s="149">
+      <c r="B20" s="48">
         <v>20204</v>
       </c>
-      <c r="C20" s="152">
+      <c r="C20" s="51">
         <v>35000</v>
       </c>
-      <c r="D20" s="81" t="s">
+      <c r="D20" s="25" t="s">
         <v>182</v>
       </c>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
-      <c r="P20" s="77"/>
+      <c r="P20" s="22"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A21" s="119" t="s">
+      <c r="A21" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="B21" s="149">
+      <c r="B21" s="48">
         <v>9264</v>
       </c>
-      <c r="C21" s="152">
+      <c r="C21" s="51">
         <v>37000</v>
       </c>
-      <c r="D21" s="81" t="s">
+      <c r="D21" s="25" t="s">
         <v>182</v>
       </c>
-      <c r="E21" s="109"/>
-      <c r="F21" s="109"/>
-      <c r="G21" s="110"/>
-      <c r="H21" s="96"/>
-      <c r="I21" s="96"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="114"/>
+      <c r="H21" s="115"/>
+      <c r="I21" s="115"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A24" s="120" t="s">
+      <c r="A24" s="116" t="s">
         <v>172</v>
       </c>
-      <c r="B24" s="84"/>
-      <c r="C24" s="84"/>
-      <c r="D24" s="84"/>
-      <c r="E24" s="84"/>
-      <c r="F24" s="84"/>
-      <c r="G24" s="84"/>
-      <c r="H24" s="84"/>
-      <c r="I24" s="84"/>
+      <c r="B24" s="117"/>
+      <c r="C24" s="117"/>
+      <c r="D24" s="117"/>
+      <c r="E24" s="117"/>
+      <c r="F24" s="117"/>
+      <c r="G24" s="117"/>
+      <c r="H24" s="117"/>
+      <c r="I24" s="117"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A25" s="121" t="s">
+      <c r="A25" s="110" t="s">
         <v>173</v>
       </c>
-      <c r="B25" s="121"/>
-      <c r="C25" s="121"/>
-      <c r="D25" s="121"/>
-      <c r="E25" s="121"/>
-      <c r="F25" s="121"/>
-      <c r="G25" s="121"/>
-      <c r="H25" s="121"/>
-      <c r="I25" s="121"/>
+      <c r="B25" s="110"/>
+      <c r="C25" s="110"/>
+      <c r="D25" s="110"/>
+      <c r="E25" s="110"/>
+      <c r="F25" s="110"/>
+      <c r="G25" s="110"/>
+      <c r="H25" s="110"/>
+      <c r="I25" s="110"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A26" s="122" t="s">
+      <c r="A26" s="109" t="s">
         <v>174</v>
       </c>
-      <c r="B26" s="122"/>
-      <c r="C26" s="122"/>
-      <c r="D26" s="122"/>
-      <c r="E26" s="122"/>
-      <c r="F26" s="122"/>
-      <c r="G26" s="122"/>
-      <c r="H26" s="122"/>
-      <c r="I26" s="122"/>
+      <c r="B26" s="109"/>
+      <c r="C26" s="109"/>
+      <c r="D26" s="109"/>
+      <c r="E26" s="109"/>
+      <c r="F26" s="109"/>
+      <c r="G26" s="109"/>
+      <c r="H26" s="109"/>
+      <c r="I26" s="109"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A27" s="121" t="s">
+      <c r="A27" s="110" t="s">
         <v>175</v>
       </c>
-      <c r="B27" s="121"/>
-      <c r="C27" s="121"/>
-      <c r="D27" s="121"/>
-      <c r="E27" s="121"/>
-      <c r="F27" s="121"/>
-      <c r="G27" s="121"/>
-      <c r="H27" s="121"/>
-      <c r="I27" s="121"/>
+      <c r="B27" s="110"/>
+      <c r="C27" s="110"/>
+      <c r="D27" s="110"/>
+      <c r="E27" s="110"/>
+      <c r="F27" s="110"/>
+      <c r="G27" s="110"/>
+      <c r="H27" s="110"/>
+      <c r="I27" s="110"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A28" s="145"/>
-      <c r="B28" s="145"/>
-      <c r="C28" s="145"/>
-      <c r="D28" s="145"/>
-      <c r="E28" s="145"/>
-      <c r="F28" s="145"/>
-      <c r="G28" s="145"/>
-      <c r="H28" s="145"/>
-      <c r="I28" s="145"/>
+      <c r="A28" s="136"/>
+      <c r="B28" s="136"/>
+      <c r="C28" s="136"/>
+      <c r="D28" s="136"/>
+      <c r="E28" s="136"/>
+      <c r="F28" s="136"/>
+      <c r="G28" s="136"/>
+      <c r="H28" s="136"/>
+      <c r="I28" s="136"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="A24:I24"/>
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A26:I26"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A5:D5"/>
     <mergeCell ref="G10:I10"/>
     <mergeCell ref="G11:I11"/>
     <mergeCell ref="G12:I12"/>
@@ -4045,10 +3997,22 @@
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A16:D16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4071,463 +4035,461 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="34.15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
     </row>
     <row r="2" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="144" t="s">
+      <c r="A2" s="145" t="s">
         <v>183</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
     </row>
     <row r="3" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="78"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="23"/>
     </row>
     <row r="5" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="153" t="s">
+      <c r="A5" s="151" t="s">
         <v>204</v>
       </c>
-      <c r="B5" s="154"/>
-      <c r="C5" s="154"/>
-      <c r="D5" s="154"/>
-      <c r="E5" s="154"/>
-      <c r="F5" s="154"/>
-      <c r="G5" s="154"/>
-      <c r="H5" s="154"/>
-      <c r="I5" s="154"/>
+      <c r="B5" s="152"/>
+      <c r="C5" s="152"/>
+      <c r="D5" s="152"/>
+      <c r="E5" s="152"/>
+      <c r="F5" s="152"/>
+      <c r="G5" s="152"/>
+      <c r="H5" s="152"/>
+      <c r="I5" s="152"/>
       <c r="N5" s="3"/>
-      <c r="O5" s="77"/>
+      <c r="O5" s="22"/>
     </row>
     <row r="6" spans="1:15" ht="25.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="111" t="s">
+      <c r="A6" s="29" t="s">
         <v>184</v>
       </c>
-      <c r="B6" s="92" t="s">
-        <v>141</v>
-      </c>
-      <c r="C6" s="92"/>
-      <c r="D6" s="92"/>
-      <c r="E6" s="92"/>
-      <c r="F6" s="92"/>
-      <c r="G6" s="124" t="s">
+      <c r="B6" s="118" t="s">
+        <v>215</v>
+      </c>
+      <c r="C6" s="118"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="118"/>
+      <c r="G6" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="H6" s="124" t="s">
+      <c r="H6" s="39" t="s">
         <v>142</v>
       </c>
-      <c r="I6" s="124" t="s">
+      <c r="I6" s="39" t="s">
         <v>186</v>
       </c>
-      <c r="K6" s="76"/>
-      <c r="L6" s="76"/>
-      <c r="M6" s="76"/>
-      <c r="N6" s="76"/>
-      <c r="O6" s="76"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="21"/>
+      <c r="N6" s="21"/>
+      <c r="O6" s="21"/>
     </row>
     <row r="7" spans="1:15" ht="57" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="115" t="s">
+      <c r="A7" s="34" t="s">
         <v>128</v>
       </c>
-      <c r="B7" s="157" t="s">
+      <c r="B7" s="153" t="s">
         <v>187</v>
       </c>
-      <c r="C7" s="157"/>
-      <c r="D7" s="157"/>
-      <c r="E7" s="157"/>
-      <c r="F7" s="157"/>
-      <c r="G7" s="103" t="s">
+      <c r="C7" s="153"/>
+      <c r="D7" s="153"/>
+      <c r="E7" s="153"/>
+      <c r="F7" s="153"/>
+      <c r="G7" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="H7" s="103" t="s">
+      <c r="H7" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="I7" s="103" t="s">
+      <c r="I7" s="28" t="s">
         <v>201</v>
       </c>
       <c r="K7" s="3"/>
-      <c r="O7" s="75"/>
+      <c r="O7" s="20"/>
     </row>
     <row r="8" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="116" t="s">
+      <c r="A8" s="35" t="s">
         <v>188</v>
       </c>
-      <c r="B8" s="157" t="s">
+      <c r="B8" s="153" t="s">
         <v>189</v>
       </c>
-      <c r="C8" s="157"/>
-      <c r="D8" s="157"/>
-      <c r="E8" s="157"/>
-      <c r="F8" s="157"/>
-      <c r="G8" s="103" t="s">
+      <c r="C8" s="153"/>
+      <c r="D8" s="153"/>
+      <c r="E8" s="153"/>
+      <c r="F8" s="153"/>
+      <c r="G8" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="H8" s="103" t="s">
+      <c r="H8" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="I8" s="103" t="s">
+      <c r="I8" s="28" t="s">
         <v>201</v>
       </c>
       <c r="K8" s="3"/>
-      <c r="O8" s="75"/>
+      <c r="O8" s="20"/>
     </row>
     <row r="9" spans="1:15" ht="45.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="116" t="s">
+      <c r="A9" s="35" t="s">
         <v>190</v>
       </c>
-      <c r="B9" s="157" t="s">
+      <c r="B9" s="153" t="s">
         <v>191</v>
       </c>
-      <c r="C9" s="157"/>
-      <c r="D9" s="157"/>
-      <c r="E9" s="157"/>
-      <c r="F9" s="157"/>
-      <c r="G9" s="103" t="s">
+      <c r="C9" s="153"/>
+      <c r="D9" s="153"/>
+      <c r="E9" s="153"/>
+      <c r="F9" s="153"/>
+      <c r="G9" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="H9" s="103" t="s">
+      <c r="H9" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="I9" s="103" t="s">
+      <c r="I9" s="28" t="s">
         <v>202</v>
       </c>
       <c r="K9" s="3"/>
-      <c r="O9" s="75"/>
+      <c r="O9" s="20"/>
     </row>
     <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="115" t="s">
+      <c r="A10" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="B10" s="157" t="s">
+      <c r="B10" s="153" t="s">
         <v>192</v>
       </c>
-      <c r="C10" s="157"/>
-      <c r="D10" s="157"/>
-      <c r="E10" s="157"/>
-      <c r="F10" s="157"/>
-      <c r="G10" s="103" t="s">
+      <c r="C10" s="153"/>
+      <c r="D10" s="153"/>
+      <c r="E10" s="153"/>
+      <c r="F10" s="153"/>
+      <c r="G10" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="H10" s="103" t="s">
+      <c r="H10" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="I10" s="103" t="s">
+      <c r="I10" s="28" t="s">
         <v>201</v>
       </c>
       <c r="K10" s="3"/>
-      <c r="O10" s="75"/>
+      <c r="O10" s="20"/>
     </row>
     <row r="11" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="115" t="s">
+      <c r="A11" s="34" t="s">
         <v>193</v>
       </c>
-      <c r="B11" s="157" t="s">
+      <c r="B11" s="153" t="s">
         <v>194</v>
       </c>
-      <c r="C11" s="157"/>
-      <c r="D11" s="157"/>
-      <c r="E11" s="157"/>
-      <c r="F11" s="157"/>
-      <c r="G11" s="103" t="s">
+      <c r="C11" s="153"/>
+      <c r="D11" s="153"/>
+      <c r="E11" s="153"/>
+      <c r="F11" s="153"/>
+      <c r="G11" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="H11" s="103" t="s">
+      <c r="H11" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="I11" s="103" t="s">
+      <c r="I11" s="28" t="s">
         <v>201</v>
       </c>
       <c r="K11" s="3"/>
-      <c r="O11" s="75"/>
+      <c r="O11" s="20"/>
     </row>
     <row r="12" spans="1:15" ht="24.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="115" t="s">
+      <c r="A12" s="34" t="s">
         <v>195</v>
       </c>
-      <c r="B12" s="157" t="s">
+      <c r="B12" s="153" t="s">
         <v>196</v>
       </c>
-      <c r="C12" s="157"/>
-      <c r="D12" s="157"/>
-      <c r="E12" s="157"/>
-      <c r="F12" s="157"/>
-      <c r="G12" s="103" t="s">
+      <c r="C12" s="153"/>
+      <c r="D12" s="153"/>
+      <c r="E12" s="153"/>
+      <c r="F12" s="153"/>
+      <c r="G12" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="H12" s="103" t="s">
+      <c r="H12" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="I12" s="146" t="s">
+      <c r="I12" s="47" t="s">
         <v>99</v>
       </c>
       <c r="K12" s="3"/>
-      <c r="O12" s="75"/>
+      <c r="O12" s="20"/>
     </row>
     <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="117" t="s">
+      <c r="A13" s="36" t="s">
         <v>197</v>
       </c>
-      <c r="B13" s="157" t="s">
+      <c r="B13" s="153" t="s">
         <v>198</v>
       </c>
-      <c r="C13" s="157"/>
-      <c r="D13" s="157"/>
-      <c r="E13" s="157"/>
-      <c r="F13" s="157"/>
-      <c r="G13" s="103" t="s">
+      <c r="C13" s="153"/>
+      <c r="D13" s="153"/>
+      <c r="E13" s="153"/>
+      <c r="F13" s="153"/>
+      <c r="G13" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="H13" s="87" t="s">
+      <c r="H13" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="I13" s="146" t="s">
+      <c r="I13" s="47" t="s">
         <v>203</v>
       </c>
       <c r="K13" s="3"/>
-      <c r="O13" s="75"/>
+      <c r="O13" s="20"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A14" s="158" t="s">
+      <c r="A14" s="52" t="s">
         <v>199</v>
       </c>
-      <c r="B14" s="83" t="s">
+      <c r="B14" s="113" t="s">
         <v>200</v>
       </c>
-      <c r="C14" s="83"/>
-      <c r="D14" s="83"/>
-      <c r="E14" s="83"/>
-      <c r="F14" s="83"/>
-      <c r="G14" s="103" t="s">
+      <c r="C14" s="113"/>
+      <c r="D14" s="113"/>
+      <c r="E14" s="113"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="H14" s="103" t="s">
+      <c r="H14" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="I14" s="146" t="s">
+      <c r="I14" s="47" t="s">
         <v>203</v>
       </c>
       <c r="K14" s="3"/>
-      <c r="O14" s="75"/>
+      <c r="O14" s="20"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B15" s="155"/>
-      <c r="C15" s="155"/>
-      <c r="D15" s="156"/>
-      <c r="E15" s="156"/>
-      <c r="F15" s="97"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="31"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="O15" s="75"/>
+      <c r="O15" s="20"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="F16" s="80"/>
-      <c r="G16" s="80"/>
-      <c r="H16" s="76"/>
-      <c r="I16" s="76"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="77"/>
+      <c r="N16" s="22"/>
     </row>
     <row r="17" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="153" t="s">
+      <c r="A17" s="151" t="s">
         <v>168</v>
       </c>
-      <c r="B17" s="154"/>
-      <c r="C17" s="154"/>
-      <c r="D17" s="154"/>
+      <c r="B17" s="152"/>
+      <c r="C17" s="152"/>
+      <c r="D17" s="152"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
-      <c r="N17" s="76"/>
-      <c r="O17" s="76"/>
-      <c r="P17" s="78"/>
+      <c r="N17" s="21"/>
+      <c r="O17" s="21"/>
+      <c r="P17" s="23"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A18" s="111" t="s">
+      <c r="A18" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="B18" s="92" t="s">
+      <c r="B18" s="118" t="s">
         <v>206</v>
       </c>
-      <c r="C18" s="92"/>
-      <c r="D18" s="92"/>
+      <c r="C18" s="118"/>
+      <c r="D18" s="118"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
-      <c r="P18" s="101"/>
+      <c r="P18" s="32"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A19" s="119" t="s">
+      <c r="A19" s="38" t="s">
         <v>190</v>
       </c>
-      <c r="B19" s="159" t="s">
+      <c r="B19" s="147" t="s">
         <v>207</v>
       </c>
-      <c r="C19" s="159"/>
-      <c r="D19" s="159"/>
+      <c r="C19" s="147"/>
+      <c r="D19" s="147"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-      <c r="P19" s="101"/>
+      <c r="P19" s="32"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A20" s="119" t="s">
+      <c r="A20" s="38" t="s">
         <v>188</v>
       </c>
-      <c r="B20" s="160" t="s">
+      <c r="B20" s="148" t="s">
         <v>208</v>
       </c>
-      <c r="C20" s="160"/>
-      <c r="D20" s="160"/>
+      <c r="C20" s="148"/>
+      <c r="D20" s="148"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
-      <c r="P20" s="102"/>
+      <c r="P20" s="33"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A21" s="119" t="s">
+      <c r="A21" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="B21" s="159" t="s">
+      <c r="B21" s="147" t="s">
         <v>209</v>
       </c>
-      <c r="C21" s="159"/>
-      <c r="D21" s="159"/>
+      <c r="C21" s="147"/>
+      <c r="D21" s="147"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
-      <c r="P21" s="77"/>
+      <c r="P21" s="22"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A22" s="119" t="s">
+      <c r="A22" s="38" t="s">
         <v>193</v>
       </c>
-      <c r="B22" s="159" t="s">
+      <c r="B22" s="147" t="s">
         <v>210</v>
       </c>
-      <c r="C22" s="159"/>
-      <c r="D22" s="159"/>
-      <c r="E22" s="109"/>
-      <c r="F22" s="109"/>
-      <c r="G22" s="110"/>
-      <c r="H22" s="96"/>
-      <c r="I22" s="96"/>
+      <c r="C22" s="147"/>
+      <c r="D22" s="147"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="114"/>
+      <c r="H22" s="115"/>
+      <c r="I22" s="115"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A23" s="161" t="s">
+      <c r="A23" s="53" t="s">
         <v>211</v>
       </c>
-      <c r="B23" s="125" t="s">
+      <c r="B23" s="149" t="s">
         <v>212</v>
       </c>
-      <c r="C23" s="125"/>
-      <c r="D23" s="125"/>
+      <c r="C23" s="149"/>
+      <c r="D23" s="149"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="B24" s="156"/>
-      <c r="C24" s="156"/>
-      <c r="D24" s="156"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A26" s="120" t="s">
+      <c r="A26" s="116" t="s">
         <v>172</v>
       </c>
-      <c r="B26" s="84"/>
-      <c r="C26" s="84"/>
-      <c r="D26" s="84"/>
-      <c r="E26" s="84"/>
-      <c r="F26" s="84"/>
-      <c r="G26" s="84"/>
-      <c r="H26" s="84"/>
-      <c r="I26" s="84"/>
+      <c r="B26" s="117"/>
+      <c r="C26" s="117"/>
+      <c r="D26" s="117"/>
+      <c r="E26" s="117"/>
+      <c r="F26" s="117"/>
+      <c r="G26" s="117"/>
+      <c r="H26" s="117"/>
+      <c r="I26" s="117"/>
     </row>
     <row r="27" spans="1:16" ht="61.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="143" t="s">
+      <c r="A27" s="150" t="s">
         <v>213</v>
       </c>
-      <c r="B27" s="143"/>
-      <c r="C27" s="143"/>
-      <c r="D27" s="143"/>
-      <c r="E27" s="143"/>
-      <c r="F27" s="143"/>
-      <c r="G27" s="143"/>
-      <c r="H27" s="143"/>
-      <c r="I27" s="143"/>
+      <c r="B27" s="150"/>
+      <c r="C27" s="150"/>
+      <c r="D27" s="150"/>
+      <c r="E27" s="150"/>
+      <c r="F27" s="150"/>
+      <c r="G27" s="150"/>
+      <c r="H27" s="150"/>
+      <c r="I27" s="150"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A28" s="145"/>
-      <c r="B28" s="145"/>
-      <c r="C28" s="145"/>
-      <c r="D28" s="145"/>
-      <c r="E28" s="145"/>
-      <c r="F28" s="145"/>
-      <c r="G28" s="145"/>
-      <c r="H28" s="145"/>
-      <c r="I28" s="145"/>
+      <c r="A28" s="136"/>
+      <c r="B28" s="136"/>
+      <c r="C28" s="136"/>
+      <c r="D28" s="136"/>
+      <c r="E28" s="136"/>
+      <c r="F28" s="136"/>
+      <c r="G28" s="136"/>
+      <c r="H28" s="136"/>
+      <c r="I28" s="136"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A29" s="145"/>
-      <c r="B29" s="145"/>
-      <c r="C29" s="145"/>
-      <c r="D29" s="145"/>
-      <c r="E29" s="145"/>
-      <c r="F29" s="145"/>
-      <c r="G29" s="145"/>
-      <c r="H29" s="145"/>
-      <c r="I29" s="145"/>
+      <c r="A29" s="136"/>
+      <c r="B29" s="136"/>
+      <c r="C29" s="136"/>
+      <c r="D29" s="136"/>
+      <c r="E29" s="136"/>
+      <c r="F29" s="136"/>
+      <c r="G29" s="136"/>
+      <c r="H29" s="136"/>
+      <c r="I29" s="136"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A30" s="145"/>
-      <c r="B30" s="145"/>
-      <c r="C30" s="145"/>
-      <c r="D30" s="145"/>
-      <c r="E30" s="145"/>
-      <c r="F30" s="145"/>
-      <c r="G30" s="145"/>
-      <c r="H30" s="145"/>
-      <c r="I30" s="145"/>
+      <c r="A30" s="136"/>
+      <c r="B30" s="136"/>
+      <c r="C30" s="136"/>
+      <c r="D30" s="136"/>
+      <c r="E30" s="136"/>
+      <c r="F30" s="136"/>
+      <c r="G30" s="136"/>
+      <c r="H30" s="136"/>
+      <c r="I30" s="136"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A27:I27"/>
     <mergeCell ref="A28:I28"/>
     <mergeCell ref="A29:I29"/>
@@ -4544,11 +4506,11 @@
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B23:D23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
